--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260901.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260901.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>64.37%</t>
+          <t>63.96%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>6.34%</t>
+          <t>6.83%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3.35%</t>
+          <t>3.36%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>2.18%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>1.76%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>1.66%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.38%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.17%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>0.97%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.87%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.77%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>0.74%</t>
+          <t>0.73%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>0.64%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>0.65%</t>
+          <t>0.63%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.59%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.55%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.52%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.44%</t>
         </is>
       </c>
     </row>
@@ -1078,46 +1078,46 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.44%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>群創</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>12,895,134</t>
+          <t>858,349</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.39%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>3481</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>群創</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>858,349</t>
+          <t>12,895,134</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1129,83 +1129,83 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>100,000</t>
+          <t>138,921</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.36%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>138,921</t>
+          <t>100,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.36%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>1,003,822</t>
+          <t>809,897</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.35%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>809,897</t>
+          <t>1,003,822</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.34%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.31%</t>
         </is>
       </c>
     </row>
@@ -1283,39 +1283,39 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>376,000</t>
+          <t>1,835,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.28%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>1,835,000</t>
+          <t>376,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.25%</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.24%</t>
         </is>
       </c>
     </row>
@@ -1452,24 +1452,24 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.19%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>4,460,578</t>
+          <t>44,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>10,615,121</t>
+          <t>4,460,578</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>44,000</t>
+          <t>10,615,121</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1591,39 +1591,39 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>583,000</t>
+          <t>146,386</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.15%</t>
+          <t>0.16%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>146,386</t>
+          <t>583,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1723,17 +1723,17 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>1,187,076</t>
+          <t>777,000</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -1745,17 +1745,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>禾伸堂</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>228,000</t>
+          <t>182,000</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -1767,17 +1767,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>182,000</t>
+          <t>805,000</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -1789,39 +1789,39 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>777,000</t>
+          <t>1,187,076</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>0.10%</t>
+          <t>0.11%</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>4,966,956</t>
+          <t>291,000</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -1833,17 +1833,17 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>320,000</t>
+          <t>4,966,956</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -1855,17 +1855,17 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>805,000</t>
+          <t>320,000</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -1877,39 +1877,39 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>華新科</t>
+          <t>禾伸堂</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>498,000</t>
+          <t>228,000</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>0.10%</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>神達</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>291,000</t>
+          <t>1,562,400</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -1921,17 +1921,17 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>神達</t>
+          <t>華新科</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>1,562,400</t>
+          <t>498,000</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -1943,17 +1943,17 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>1,004,121</t>
+          <t>115,000</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -1987,17 +1987,17 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>115,000</t>
+          <t>1,004,121</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -2009,17 +2009,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>157,000</t>
+          <t>65,538</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>332,000</t>
+          <t>157,000</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2053,17 +2053,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>65,538</t>
+          <t>332,000</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2119,17 +2119,17 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>德律</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>254,000</t>
+          <t>681,000</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -2141,17 +2141,17 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>德律</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>681,000</t>
+          <t>254,000</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -2163,17 +2163,17 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>台勝科</t>
+          <t>新唐</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>115,000</t>
+          <t>336,000</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -2207,17 +2207,17 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>4919</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>新唐</t>
+          <t>台勝科</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>336,000</t>
+          <t>115,000</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>280,974,002</t>
+          <t>280,265,547</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr"/>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>343,562,454</t>
+          <t>361,858,454</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr"/>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>373,977,873</t>
+          <t>30,916,792</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr"/>
@@ -2293,7 +2293,7 @@
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>342,394,877</t>
+          <t>2,049,169</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr"/>
